--- a/data/source/weekly/cs-en-us-045pct.xlsx
+++ b/data/source/weekly/cs-en-us-045pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,8 +869,8 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -878,14 +878,14 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="14">
-        <v>-100</v>
+      <c r="L14" s="15">
+        <v>0</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="14">
-        <v>-100</v>
+      <c r="N14" s="15">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,243 +895,243 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>4</v>
+      </c>
+      <c r="G15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="15">
+      <c r="H15" s="15">
+        <v>300</v>
+      </c>
+      <c r="I15" s="14">
+        <v>5</v>
+      </c>
+      <c r="J15" s="14">
         <v>3</v>
       </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
-        <v>200</v>
-      </c>
-      <c r="I15" s="15">
-        <v>4</v>
-      </c>
-      <c r="J15" s="15">
-        <v>3</v>
-      </c>
-      <c r="K15" s="14">
-        <v>33.333333333333</v>
-      </c>
-      <c r="L15" s="14">
-        <v>0</v>
-      </c>
-      <c r="M15" s="14">
-        <v>33.333333333333</v>
-      </c>
-      <c r="N15" s="14">
-        <v>33.333333333333</v>
+      <c r="K15" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="L15" s="15">
+        <v>25</v>
+      </c>
+      <c r="M15" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="N15" s="15">
+        <v>66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>4</v>
-      </c>
-      <c r="D16" s="15">
-        <v>2</v>
-      </c>
-      <c r="E16" s="14">
-        <v>100</v>
-      </c>
-      <c r="F16" s="15">
-        <v>12</v>
-      </c>
-      <c r="G16" s="15">
+      <c r="C16" s="14">
+        <v>7</v>
+      </c>
+      <c r="D16" s="14">
+        <v>3</v>
+      </c>
+      <c r="E16" s="15">
+        <v>133.333333333333</v>
+      </c>
+      <c r="F16" s="14">
         <v>18</v>
       </c>
-      <c r="H16" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="I16" s="15">
+      <c r="G16" s="14">
         <v>18</v>
       </c>
-      <c r="J16" s="15">
-        <v>30</v>
-      </c>
-      <c r="K16" s="14">
-        <v>-40</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-18.181818181818</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-67.272727272727</v>
+      <c r="H16" s="15">
+        <v>0</v>
+      </c>
+      <c r="I16" s="14">
+        <v>25</v>
+      </c>
+      <c r="J16" s="14">
+        <v>33</v>
+      </c>
+      <c r="K16" s="15">
+        <v>-24.242424242424</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-13.793103448275</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-19.354838709677</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-59.016393442622</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>5</v>
-      </c>
-      <c r="D17" s="15">
-        <v>6</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-16.666666666666</v>
-      </c>
-      <c r="F17" s="15">
-        <v>26</v>
-      </c>
-      <c r="G17" s="15">
-        <v>20</v>
-      </c>
-      <c r="H17" s="14">
-        <v>30</v>
-      </c>
-      <c r="I17" s="15">
+      <c r="C17" s="14">
+        <v>1</v>
+      </c>
+      <c r="D17" s="14">
+        <v>8</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-87.5</v>
+      </c>
+      <c r="F17" s="14">
+        <v>23</v>
+      </c>
+      <c r="G17" s="14">
+        <v>21</v>
+      </c>
+      <c r="H17" s="15">
+        <v>9.523809523809</v>
+      </c>
+      <c r="I17" s="14">
+        <v>39</v>
+      </c>
+      <c r="J17" s="14">
         <v>38</v>
       </c>
-      <c r="J17" s="15">
-        <v>30</v>
-      </c>
-      <c r="K17" s="14">
-        <v>26.666666666666</v>
-      </c>
-      <c r="L17" s="14">
-        <v>11.764705882352</v>
-      </c>
-      <c r="M17" s="14">
-        <v>80.952380952380</v>
-      </c>
-      <c r="N17" s="14">
-        <v>26.666666666666</v>
+      <c r="K17" s="15">
+        <v>2.631578947368</v>
+      </c>
+      <c r="L17" s="15">
+        <v>-2.5</v>
+      </c>
+      <c r="M17" s="15">
+        <v>62.5</v>
+      </c>
+      <c r="N17" s="15">
+        <v>11.428571428571</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
-      </c>
-      <c r="D18" s="15">
+      <c r="C18" s="14">
+        <v>4</v>
+      </c>
+      <c r="D18" s="14">
         <v>3</v>
       </c>
-      <c r="E18" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F18" s="15">
-        <v>6</v>
-      </c>
-      <c r="G18" s="15">
+      <c r="E18" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="F18" s="14">
+        <v>8</v>
+      </c>
+      <c r="G18" s="14">
         <v>14</v>
       </c>
-      <c r="H18" s="14">
-        <v>-57.142857142857</v>
-      </c>
-      <c r="I18" s="15">
-        <v>8</v>
-      </c>
-      <c r="J18" s="15">
-        <v>17</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-52.941176470588</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-27.272727272727</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-75</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-91.836734693877</v>
+      <c r="H18" s="15">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="I18" s="14">
+        <v>12</v>
+      </c>
+      <c r="J18" s="14">
+        <v>20</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-40</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-64.705882352941</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-89.285714285714</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>7</v>
-      </c>
-      <c r="D19" s="15">
-        <v>12</v>
-      </c>
-      <c r="E19" s="14">
-        <v>-41.666666666666</v>
-      </c>
-      <c r="F19" s="15">
-        <v>49</v>
-      </c>
-      <c r="G19" s="15">
-        <v>35</v>
-      </c>
-      <c r="H19" s="14">
+      <c r="C19" s="14">
+        <v>9</v>
+      </c>
+      <c r="D19" s="14">
+        <v>13</v>
+      </c>
+      <c r="E19" s="15">
+        <v>-30.769230769230</v>
+      </c>
+      <c r="F19" s="14">
+        <v>36</v>
+      </c>
+      <c r="G19" s="14">
         <v>40</v>
       </c>
-      <c r="I19" s="15">
-        <v>70</v>
-      </c>
-      <c r="J19" s="15">
-        <v>51</v>
-      </c>
-      <c r="K19" s="14">
-        <v>37.254901960784</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-5.405405405405</v>
-      </c>
-      <c r="M19" s="14">
-        <v>55.555555555555</v>
-      </c>
-      <c r="N19" s="14">
-        <v>25</v>
+      <c r="H19" s="15">
+        <v>-10</v>
+      </c>
+      <c r="I19" s="14">
+        <v>78</v>
+      </c>
+      <c r="J19" s="14">
+        <v>64</v>
+      </c>
+      <c r="K19" s="15">
+        <v>21.875</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-7.142857142857</v>
+      </c>
+      <c r="M19" s="15">
+        <v>56</v>
+      </c>
+      <c r="N19" s="15">
+        <v>23.809523809523</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>15</v>
-      </c>
-      <c r="D20" s="15">
-        <v>9</v>
-      </c>
-      <c r="E20" s="14">
-        <v>66.666666666666</v>
-      </c>
-      <c r="F20" s="15">
-        <v>34</v>
-      </c>
-      <c r="G20" s="15">
-        <v>36</v>
-      </c>
-      <c r="H20" s="14">
-        <v>-5.555555555555</v>
-      </c>
-      <c r="I20" s="15">
-        <v>45</v>
-      </c>
-      <c r="J20" s="15">
-        <v>58</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-22.413793103448</v>
-      </c>
-      <c r="L20" s="14">
-        <v>4.651162790697</v>
-      </c>
-      <c r="M20" s="14">
-        <v>200</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-77.832512315270</v>
+      <c r="C20" s="14">
+        <v>12</v>
+      </c>
+      <c r="D20" s="14">
+        <v>10</v>
+      </c>
+      <c r="E20" s="15">
+        <v>20</v>
+      </c>
+      <c r="F20" s="14">
+        <v>40</v>
+      </c>
+      <c r="G20" s="14">
+        <v>41</v>
+      </c>
+      <c r="H20" s="15">
+        <v>-2.439024390243</v>
+      </c>
+      <c r="I20" s="14">
+        <v>57</v>
+      </c>
+      <c r="J20" s="14">
+        <v>68</v>
+      </c>
+      <c r="K20" s="15">
+        <v>-16.176470588235</v>
+      </c>
+      <c r="L20" s="15">
+        <v>21.276595744680</v>
+      </c>
+      <c r="M20" s="15">
+        <v>256.25</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-76.446280991735</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E21" s="18">
-        <v>-3.030303030303</v>
+        <v>-10.810810810810</v>
       </c>
       <c r="F21" s="17">
         <v>130</v>
       </c>
       <c r="G21" s="17">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H21" s="18">
-        <v>4.838709677419</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="I21" s="17">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="J21" s="17">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.174603174603</v>
+        <v>-3.982300884955</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.174603174603</v>
+        <v>-0.913242009132</v>
       </c>
       <c r="M21" s="18">
-        <v>27.972027972028</v>
+        <v>37.341772151898</v>
       </c>
       <c r="N21" s="18">
-        <v>-58.968609865470</v>
+        <v>-58.027079303675</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,34 +1182,34 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="15">
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-100</v>
+      </c>
+      <c r="I22" s="14">
         <v>2</v>
       </c>
-      <c r="J22" s="15">
-        <v>1</v>
-      </c>
-      <c r="K22" s="14">
-        <v>100</v>
+      <c r="J22" s="14">
+        <v>2</v>
+      </c>
+      <c r="K22" s="15">
+        <v>0</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M22" s="14">
+      <c r="M22" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="15">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14">
-        <v>0</v>
-      </c>
-      <c r="F23" s="15">
-        <v>1</v>
-      </c>
-      <c r="G23" s="15">
-        <v>5</v>
-      </c>
-      <c r="H23" s="14">
-        <v>-80</v>
-      </c>
-      <c r="I23" s="15">
+      <c r="G23" s="14">
+        <v>6</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-83.333333333333</v>
+      </c>
+      <c r="I23" s="14">
         <v>2</v>
       </c>
-      <c r="J23" s="15">
-        <v>7</v>
-      </c>
-      <c r="K23" s="14">
-        <v>-71.428571428571</v>
-      </c>
-      <c r="L23" s="14">
-        <v>-71.428571428571</v>
-      </c>
-      <c r="M23" s="14">
-        <v>-33.333333333333</v>
+      <c r="J23" s="14">
+        <v>9</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-77.777777777777</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-81.818181818181</v>
+      </c>
+      <c r="M23" s="15">
+        <v>-50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="14">
         <v>17</v>
       </c>
-      <c r="D24" s="15">
-        <v>14</v>
-      </c>
-      <c r="E24" s="14">
-        <v>21.428571428571</v>
-      </c>
-      <c r="F24" s="15">
-        <v>98</v>
-      </c>
-      <c r="G24" s="15">
-        <v>87</v>
-      </c>
-      <c r="H24" s="14">
-        <v>12.643678160919</v>
-      </c>
-      <c r="I24" s="15">
-        <v>128</v>
-      </c>
-      <c r="J24" s="15">
-        <v>121</v>
-      </c>
-      <c r="K24" s="14">
-        <v>5.785123966942</v>
-      </c>
-      <c r="L24" s="14">
-        <v>0.787401574803</v>
-      </c>
-      <c r="M24" s="14">
-        <v>3.225806451612</v>
+      <c r="D24" s="14">
+        <v>13</v>
+      </c>
+      <c r="E24" s="15">
+        <v>30.769230769230</v>
+      </c>
+      <c r="F24" s="14">
+        <v>85</v>
+      </c>
+      <c r="G24" s="14">
+        <v>69</v>
+      </c>
+      <c r="H24" s="15">
+        <v>23.188405797101</v>
+      </c>
+      <c r="I24" s="14">
+        <v>144</v>
+      </c>
+      <c r="J24" s="14">
+        <v>134</v>
+      </c>
+      <c r="K24" s="15">
+        <v>7.462686567164</v>
+      </c>
+      <c r="L24" s="15">
+        <v>-11.656441717791</v>
+      </c>
+      <c r="M24" s="15">
+        <v>5.109489051094</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="14">
         <v>11</v>
       </c>
-      <c r="D25" s="15">
-        <v>9</v>
-      </c>
-      <c r="E25" s="14">
-        <v>22.222222222222</v>
-      </c>
-      <c r="F25" s="15">
-        <v>49</v>
-      </c>
-      <c r="G25" s="15">
-        <v>49</v>
-      </c>
-      <c r="H25" s="14">
-        <v>0</v>
-      </c>
-      <c r="I25" s="15">
-        <v>63</v>
-      </c>
-      <c r="J25" s="15">
-        <v>64</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-1.5625</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-20.253164556962</v>
+      <c r="D25" s="14">
+        <v>7</v>
+      </c>
+      <c r="E25" s="15">
+        <v>57.142857142857</v>
+      </c>
+      <c r="F25" s="14">
+        <v>43</v>
+      </c>
+      <c r="G25" s="14">
+        <v>34</v>
+      </c>
+      <c r="H25" s="15">
+        <v>26.470588235294</v>
+      </c>
+      <c r="I25" s="14">
+        <v>74</v>
+      </c>
+      <c r="J25" s="14">
+        <v>71</v>
+      </c>
+      <c r="K25" s="15">
+        <v>4.225352112676</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-26.732673267326</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="14">
         <v>15</v>
       </c>
-      <c r="D26" s="15">
-        <v>11</v>
-      </c>
-      <c r="E26" s="14">
-        <v>36.363636363636</v>
-      </c>
-      <c r="F26" s="15">
-        <v>45</v>
-      </c>
-      <c r="G26" s="15">
-        <v>32</v>
-      </c>
-      <c r="H26" s="14">
-        <v>40.625</v>
-      </c>
-      <c r="I26" s="15">
-        <v>63</v>
-      </c>
-      <c r="J26" s="15">
-        <v>44</v>
-      </c>
-      <c r="K26" s="14">
-        <v>43.181818181818</v>
-      </c>
-      <c r="L26" s="14">
-        <v>36.956521739130</v>
-      </c>
-      <c r="M26" s="14">
-        <v>65.789473684210</v>
+      <c r="D26" s="14">
+        <v>8</v>
+      </c>
+      <c r="E26" s="15">
+        <v>87.5</v>
+      </c>
+      <c r="F26" s="14">
+        <v>50</v>
+      </c>
+      <c r="G26" s="14">
+        <v>33</v>
+      </c>
+      <c r="H26" s="15">
+        <v>51.515151515151</v>
+      </c>
+      <c r="I26" s="14">
+        <v>78</v>
+      </c>
+      <c r="J26" s="14">
+        <v>52</v>
+      </c>
+      <c r="K26" s="15">
+        <v>50</v>
+      </c>
+      <c r="L26" s="15">
+        <v>20</v>
+      </c>
+      <c r="M26" s="15">
+        <v>73.333333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="15">
+      <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="15">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>5</v>
+      </c>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>400</v>
+      </c>
+      <c r="I27" s="14">
+        <v>6</v>
+      </c>
+      <c r="J27" s="14">
         <v>3</v>
       </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
-      <c r="H27" s="14">
-        <v>200</v>
-      </c>
-      <c r="I27" s="15">
-        <v>4</v>
-      </c>
-      <c r="J27" s="15">
-        <v>3</v>
-      </c>
-      <c r="K27" s="14">
-        <v>33.333333333333</v>
-      </c>
-      <c r="L27" s="14">
-        <v>0</v>
+      <c r="K27" s="15">
+        <v>100</v>
+      </c>
+      <c r="L27" s="15">
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>0</v>
-      </c>
-      <c r="F28" s="15">
-        <v>3</v>
-      </c>
-      <c r="G28" s="15">
-        <v>10</v>
-      </c>
-      <c r="H28" s="14">
-        <v>-70</v>
-      </c>
-      <c r="I28" s="15">
-        <v>6</v>
-      </c>
-      <c r="J28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>2</v>
+      </c>
+      <c r="G28" s="14">
+        <v>5</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-60</v>
+      </c>
+      <c r="I28" s="14">
+        <v>5</v>
+      </c>
+      <c r="J28" s="14">
         <v>12</v>
       </c>
-      <c r="K28" s="14">
-        <v>-50</v>
-      </c>
-      <c r="L28" s="14">
-        <v>0</v>
+      <c r="K28" s="15">
+        <v>-58.333333333333</v>
+      </c>
+      <c r="L28" s="15">
+        <v>-28.571428571428</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,7 +1475,7 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="15">
+      <c r="F29" s="14">
         <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
@@ -1484,22 +1484,22 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I29" s="14">
         <v>1</v>
       </c>
-      <c r="J29" s="15">
+      <c r="J29" s="14">
         <v>1</v>
       </c>
-      <c r="K29" s="14">
+      <c r="K29" s="15">
         <v>0</v>
       </c>
-      <c r="L29" s="14">
+      <c r="L29" s="15">
         <v>0</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="14">
+      <c r="N29" s="15">
         <v>-80</v>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="15">
+      <c r="F30" s="14">
         <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
@@ -1525,22 +1525,22 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I30" s="14">
         <v>1</v>
       </c>
-      <c r="J30" s="15">
+      <c r="J30" s="14">
         <v>1</v>
       </c>
-      <c r="K30" s="14">
+      <c r="K30" s="15">
         <v>0</v>
       </c>
-      <c r="L30" s="14">
+      <c r="L30" s="15">
         <v>0</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N30" s="14">
+      <c r="N30" s="15">
         <v>-80</v>
       </c>
     </row>
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>17</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>17</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>4</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>5</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>10</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>100</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>150</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-41.176470588235</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-41.176470588235</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
-        <v>21</v>
-      </c>
-      <c r="E40" s="15">
+      <c r="C40" s="14">
+        <v>21</v>
+      </c>
+      <c r="E40" s="14">
         <v>22</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>29</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>22</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>36</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>63.636363636363</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>24.137931034482</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>63.636363636363</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>71.428571428571</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>505</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>457</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>318</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>212</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>201</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-5.188679245283</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-36.792452830188</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-56.017505470459</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-60.198019801980</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>197</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>231</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>238</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>183</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>372</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>103.27868852459</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>56.302521008403</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>61.038961038961</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>88.832487309644</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>824</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>803</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>387</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>370</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>139</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-62.432432432432</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-64.082687338501</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-82.689912826899</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-83.131067961165</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>473</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>415</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>412</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>472</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>796</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>68.644067796610</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>93.203883495145</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>91.807228915662</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>68.287526427061</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>2690</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>2185</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>1089</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>629</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>562</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-10.651828298887</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-48.393021120293</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-74.279176201373</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-79.107806691449</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-045pct.xlsx
+++ b/data/source/weekly/cs-en-us-045pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>0</v>
       </c>
       <c r="L14" s="15">
         <v>0</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="N15" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>133.333333333333</v>
+        <v>25</v>
       </c>
       <c r="F16" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G16" s="14">
         <v>18</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I16" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J16" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K16" s="15">
-        <v>-24.242424242424</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="L16" s="15">
-        <v>-13.793103448275</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="M16" s="15">
-        <v>-19.354838709677</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="N16" s="15">
-        <v>-59.016393442622</v>
+        <v>-56.521739130434</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-87.5</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H17" s="15">
-        <v>9.523809523809</v>
+        <v>31.578947368421</v>
       </c>
       <c r="I17" s="14">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J17" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K17" s="15">
-        <v>2.631578947368</v>
+        <v>9.756097560975</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.5</v>
+        <v>-8.163265306122</v>
       </c>
       <c r="M17" s="15">
-        <v>62.5</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N17" s="15">
-        <v>11.428571428571</v>
+        <v>18.421052631578</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>-42.857142857142</v>
+        <v>-37.5</v>
       </c>
       <c r="I18" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J18" s="14">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K18" s="15">
-        <v>-40</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L18" s="15">
-        <v>-14.285714285714</v>
+        <v>6.666666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.705882352941</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.285714285714</v>
+        <v>-87.301587301587</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
         <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-30.769230769230</v>
+        <v>15.384615384615</v>
       </c>
       <c r="F19" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G19" s="14">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H19" s="15">
-        <v>-10</v>
+        <v>-14.893617021276</v>
       </c>
       <c r="I19" s="14">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="J19" s="14">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="K19" s="15">
-        <v>21.875</v>
+        <v>20.779220779220</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.142857142857</v>
+        <v>-3.125</v>
       </c>
       <c r="M19" s="15">
-        <v>56</v>
+        <v>66.071428571428</v>
       </c>
       <c r="N19" s="15">
-        <v>23.809523809523</v>
+        <v>36.764705882352</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="F20" s="14">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G20" s="14">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H20" s="15">
-        <v>-2.439024390243</v>
+        <v>38.235294117647</v>
       </c>
       <c r="I20" s="14">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="J20" s="14">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K20" s="15">
-        <v>-16.176470588235</v>
+        <v>-4.109589041095</v>
       </c>
       <c r="L20" s="15">
-        <v>21.276595744680</v>
+        <v>29.629629629629</v>
       </c>
       <c r="M20" s="15">
-        <v>256.25</v>
+        <v>233.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-76.446280991735</v>
+        <v>-75.945017182130</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D21" s="17">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E21" s="18">
-        <v>-10.810810810810</v>
+        <v>37.5</v>
       </c>
       <c r="F21" s="17">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="G21" s="17">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.703703703703</v>
+        <v>5.882352941176</v>
       </c>
       <c r="I21" s="17">
-        <v>217</v>
+        <v>261</v>
       </c>
       <c r="J21" s="17">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.982300884955</v>
+        <v>1.162790697674</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.913242009132</v>
+        <v>1.953125</v>
       </c>
       <c r="M21" s="18">
-        <v>37.341772151898</v>
+        <v>42.622950819672</v>
       </c>
       <c r="N21" s="18">
-        <v>-58.027079303675</v>
+        <v>-56.208053691275</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1206,8 +1206,8 @@
       <c r="K22" s="15">
         <v>0</v>
       </c>
-      <c r="L22" s="13" t="s">
-        <v>21</v>
+      <c r="L22" s="15">
+        <v>100</v>
       </c>
       <c r="M22" s="15">
         <v>-33.333333333333</v>
@@ -1224,7 +1224,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
         <v>-100</v>
@@ -1233,19 +1233,19 @@
         <v>1</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I23" s="14">
         <v>2</v>
       </c>
       <c r="J23" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K23" s="15">
-        <v>-77.777777777777</v>
+        <v>-80</v>
       </c>
       <c r="L23" s="15">
         <v>-81.818181818181</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E24" s="15">
-        <v>30.769230769230</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G24" s="14">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H24" s="15">
-        <v>23.188405797101</v>
+        <v>-7.954545454545</v>
       </c>
       <c r="I24" s="14">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="J24" s="14">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="K24" s="15">
-        <v>7.462686567164</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="L24" s="15">
-        <v>-11.656441717791</v>
+        <v>-14.0625</v>
       </c>
       <c r="M24" s="15">
-        <v>5.109489051094</v>
+        <v>5.769230769230</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E25" s="15">
-        <v>57.142857142857</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="F25" s="14">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G25" s="14">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="H25" s="15">
-        <v>26.470588235294</v>
+        <v>4.255319148936</v>
       </c>
       <c r="I25" s="14">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="J25" s="14">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="K25" s="15">
-        <v>4.225352112676</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="L25" s="15">
-        <v>-26.732673267326</v>
+        <v>-20.353982300885</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>87.5</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F26" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G26" s="14">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>51.515151515151</v>
+        <v>23.255813953488</v>
       </c>
       <c r="I26" s="14">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J26" s="14">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="K26" s="15">
-        <v>50</v>
+        <v>36.923076923076</v>
       </c>
       <c r="L26" s="15">
-        <v>20</v>
+        <v>14.102564102564</v>
       </c>
       <c r="M26" s="15">
-        <v>73.333333333333</v>
+        <v>64.814814814814</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
         <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="I28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>-58.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L28" s="15">
-        <v>-28.571428571428</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="14">
+      <c r="D29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="E29" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L29" s="15">
         <v>0</v>
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="14">
+      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="E30" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="15">
         <v>0</v>

--- a/data/source/weekly/cs-en-us-045pct.xlsx
+++ b/data/source/weekly/cs-en-us-045pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
+        <v>3</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>-25</v>
       </c>
       <c r="I15" s="14">
+        <v>8</v>
+      </c>
+      <c r="J15" s="14">
         <v>6</v>
       </c>
-      <c r="J15" s="14">
-        <v>3</v>
-      </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M15" s="15">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N15" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="F16" s="14">
         <v>19</v>
       </c>
       <c r="G16" s="14">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>5.555555555555</v>
+        <v>90</v>
       </c>
       <c r="I16" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J16" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K16" s="15">
-        <v>-18.918918918918</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="L16" s="15">
-        <v>-18.918918918918</v>
+        <v>-23.255813953488</v>
       </c>
       <c r="M16" s="15">
-        <v>-18.918918918918</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="N16" s="15">
-        <v>-56.521739130434</v>
+        <v>-55.405405405405</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="F17" s="14">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G17" s="14">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H17" s="15">
-        <v>31.578947368421</v>
+        <v>-61.290322580645</v>
       </c>
       <c r="I17" s="14">
         <v>45</v>
       </c>
       <c r="J17" s="14">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="K17" s="15">
-        <v>9.756097560975</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.163265306122</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M17" s="15">
-        <v>66.666666666666</v>
+        <v>60.714285714285</v>
       </c>
       <c r="N17" s="15">
-        <v>18.421052631578</v>
+        <v>-2.173913043478</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>4</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
         <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-37.5</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="I18" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" s="14">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K18" s="15">
-        <v>-38.461538461538</v>
+        <v>-51.428571428571</v>
       </c>
       <c r="L18" s="15">
-        <v>6.666666666666</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.894736842105</v>
+        <v>-61.363636363636</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.301587301587</v>
+        <v>-88.028169014084</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>15.384615384615</v>
+        <v>80</v>
       </c>
       <c r="F19" s="14">
         <v>40</v>
       </c>
       <c r="G19" s="14">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H19" s="15">
-        <v>-14.893617021276</v>
+        <v>-6.976744186046</v>
       </c>
       <c r="I19" s="14">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J19" s="14">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K19" s="15">
-        <v>20.779220779220</v>
+        <v>25.609756097561</v>
       </c>
       <c r="L19" s="15">
-        <v>-3.125</v>
+        <v>-3.738317757009</v>
       </c>
       <c r="M19" s="15">
-        <v>66.071428571428</v>
+        <v>66.129032258064</v>
       </c>
       <c r="N19" s="15">
-        <v>36.764705882352</v>
+        <v>39.189189189189</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>4</v>
+      </c>
+      <c r="D20" s="14">
         <v>13</v>
       </c>
-      <c r="D20" s="14">
-        <v>5</v>
-      </c>
       <c r="E20" s="15">
-        <v>160</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="F20" s="14">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G20" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H20" s="15">
-        <v>38.235294117647</v>
+        <v>18.918918918918</v>
       </c>
       <c r="I20" s="14">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J20" s="14">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="K20" s="15">
-        <v>-4.109589041095</v>
+        <v>-13.953488372093</v>
       </c>
       <c r="L20" s="15">
-        <v>29.629629629629</v>
+        <v>17.460317460317</v>
       </c>
       <c r="M20" s="15">
-        <v>233.333333333333</v>
+        <v>196</v>
       </c>
       <c r="N20" s="15">
-        <v>-75.945017182130</v>
+        <v>-76.802507836990</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E21" s="18">
-        <v>37.5</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F21" s="17">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="G21" s="17">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="H21" s="18">
-        <v>5.882352941176</v>
+        <v>-12.244897959183</v>
       </c>
       <c r="I21" s="17">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J21" s="17">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="K21" s="18">
-        <v>1.162790697674</v>
+        <v>-7.260726072607</v>
       </c>
       <c r="L21" s="18">
-        <v>1.953125</v>
+        <v>-4.095563139931</v>
       </c>
       <c r="M21" s="18">
-        <v>42.622950819672</v>
+        <v>38.423645320197</v>
       </c>
       <c r="N21" s="18">
-        <v>-56.208053691275</v>
+        <v>-57.359635811836</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,20 +1223,20 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>1</v>
       </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-85.714285714285</v>
+        <v>-75</v>
       </c>
       <c r="I23" s="14">
         <v>2</v>
@@ -1251,7 +1251,7 @@
         <v>-81.818181818181</v>
       </c>
       <c r="M23" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D24" s="14">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>-41.666666666666</v>
+        <v>40.909090909090</v>
       </c>
       <c r="F24" s="14">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G24" s="14">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H24" s="15">
-        <v>-7.954545454545</v>
+        <v>1.176470588235</v>
       </c>
       <c r="I24" s="14">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="J24" s="14">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.941176470588</v>
+        <v>2.083333333333</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.0625</v>
+        <v>-15.517241379310</v>
       </c>
       <c r="M24" s="15">
-        <v>5.769230769230</v>
+        <v>9.497206703910</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D25" s="14">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E25" s="15">
-        <v>-30.434782608695</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G25" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H25" s="15">
-        <v>4.255319148936</v>
+        <v>17.647058823529</v>
       </c>
       <c r="I25" s="14">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="J25" s="14">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="K25" s="15">
-        <v>-4.255319148936</v>
+        <v>5.660377358490</v>
       </c>
       <c r="L25" s="15">
-        <v>-20.353982300885</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-15.384615384615</v>
+        <v>-12.5</v>
       </c>
       <c r="F26" s="14">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G26" s="14">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H26" s="15">
-        <v>23.255813953488</v>
+        <v>22.5</v>
       </c>
       <c r="I26" s="14">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="J26" s="14">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K26" s="15">
-        <v>36.923076923076</v>
+        <v>32.876712328767</v>
       </c>
       <c r="L26" s="15">
-        <v>14.102564102564</v>
+        <v>4.301075268817</v>
       </c>
       <c r="M26" s="15">
-        <v>64.814814814814</v>
+        <v>64.406779661017</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>4</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>-40</v>
       </c>
       <c r="I27" s="14">
+        <v>8</v>
+      </c>
+      <c r="J27" s="14">
         <v>7</v>
       </c>
-      <c r="J27" s="14">
-        <v>3</v>
-      </c>
       <c r="K27" s="15">
-        <v>133.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L27" s="15">
-        <v>40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
+        <v>4</v>
+      </c>
+      <c r="G28" s="14">
         <v>3</v>
       </c>
-      <c r="G28" s="14">
-        <v>5</v>
-      </c>
       <c r="H28" s="15">
-        <v>-40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="14">
         <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L28" s="15">
-        <v>-22.222222222222</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>3</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>3</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>3</v>
+      </c>
+      <c r="K31" s="15">
+        <v>-100</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>
@@ -1634,8 +1634,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-045pct.xlsx
+++ b/data/source/weekly/cs-en-us-045pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -860,14 +860,14 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>4</v>
+      </c>
+      <c r="G15" s="14">
         <v>3</v>
       </c>
-      <c r="E15" s="15">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
-      </c>
-      <c r="G15" s="14">
-        <v>4</v>
-      </c>
       <c r="H15" s="15">
-        <v>-25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
         <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M15" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="N15" s="15">
-        <v>166.666666666667</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>200</v>
+        <v>-80</v>
       </c>
       <c r="F16" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H16" s="15">
-        <v>90</v>
+        <v>23.076923076923</v>
       </c>
       <c r="I16" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J16" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K16" s="15">
-        <v>-13.157894736842</v>
+        <v>-20.930232558139</v>
       </c>
       <c r="L16" s="15">
-        <v>-23.255813953488</v>
+        <v>-27.659574468085</v>
       </c>
       <c r="M16" s="15">
-        <v>-15.384615384615</v>
+        <v>-20.930232558139</v>
       </c>
       <c r="N16" s="15">
-        <v>-55.405405405405</v>
+        <v>-58.536585365853</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>-85.714285714285</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F17" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H17" s="15">
-        <v>-61.290322580645</v>
+        <v>-52.777777777777</v>
       </c>
       <c r="I17" s="14">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="J17" s="14">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="K17" s="15">
-        <v>-18.181818181818</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L17" s="15">
-        <v>-18.181818181818</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>60.714285714285</v>
+        <v>71.875</v>
       </c>
       <c r="N17" s="15">
-        <v>-2.173913043478</v>
+        <v>14.583333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H18" s="15">
-        <v>-52.380952380952</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K18" s="15">
-        <v>-51.428571428571</v>
+        <v>-51.351351351351</v>
       </c>
       <c r="L18" s="15">
-        <v>-10.526315789473</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M18" s="15">
-        <v>-61.363636363636</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.028169014084</v>
+        <v>-88.679245283018</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>80</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="G19" s="14">
         <v>43</v>
       </c>
       <c r="H19" s="15">
-        <v>-6.976744186046</v>
+        <v>23.255813953488</v>
       </c>
       <c r="I19" s="14">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="J19" s="14">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K19" s="15">
-        <v>25.609756097561</v>
+        <v>30.851063829787</v>
       </c>
       <c r="L19" s="15">
-        <v>-3.738317757009</v>
+        <v>-0.806451612903</v>
       </c>
       <c r="M19" s="15">
-        <v>66.129032258064</v>
+        <v>80.882352941176</v>
       </c>
       <c r="N19" s="15">
-        <v>39.189189189189</v>
+        <v>51.851851851851</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>12</v>
+      </c>
+      <c r="D20" s="14">
         <v>4</v>
       </c>
-      <c r="D20" s="14">
-        <v>13</v>
-      </c>
       <c r="E20" s="15">
-        <v>-69.230769230769</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G20" s="14">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H20" s="15">
-        <v>18.918918918918</v>
+        <v>28.125</v>
       </c>
       <c r="I20" s="14">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="J20" s="14">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K20" s="15">
-        <v>-13.953488372093</v>
+        <v>-4.444444444444</v>
       </c>
       <c r="L20" s="15">
-        <v>17.460317460317</v>
+        <v>14.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>196</v>
+        <v>218.518518518519</v>
       </c>
       <c r="N20" s="15">
-        <v>-76.802507836990</v>
+        <v>-75.072463768115</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="D21" s="17">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="E21" s="18">
-        <v>-55.555555555555</v>
+        <v>32.352941176470</v>
       </c>
       <c r="F21" s="17">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="G21" s="17">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.244897959183</v>
+        <v>-4.729729729729</v>
       </c>
       <c r="I21" s="17">
-        <v>281</v>
+        <v>326</v>
       </c>
       <c r="J21" s="17">
-        <v>303</v>
+        <v>337</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.260726072607</v>
+        <v>-3.264094955489</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.095563139931</v>
+        <v>-2.102102102102</v>
       </c>
       <c r="M21" s="18">
-        <v>38.423645320197</v>
+        <v>44.247787610619</v>
       </c>
       <c r="N21" s="18">
-        <v>-57.359635811836</v>
+        <v>-54.722222222222</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
         <v>-33.333333333333</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1233,25 +1233,25 @@
         <v>1</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" s="14">
         <v>10</v>
       </c>
       <c r="K23" s="15">
-        <v>-80</v>
+        <v>-70</v>
       </c>
       <c r="L23" s="15">
-        <v>-81.818181818181</v>
+        <v>-75</v>
       </c>
       <c r="M23" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E24" s="15">
-        <v>40.909090909090</v>
+        <v>60</v>
       </c>
       <c r="F24" s="14">
+        <v>92</v>
+      </c>
+      <c r="G24" s="14">
         <v>86</v>
       </c>
-      <c r="G24" s="14">
-        <v>85</v>
-      </c>
       <c r="H24" s="15">
-        <v>1.176470588235</v>
+        <v>6.976744186046</v>
       </c>
       <c r="I24" s="14">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="J24" s="14">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="K24" s="15">
-        <v>2.083333333333</v>
+        <v>5.797101449275</v>
       </c>
       <c r="L24" s="15">
-        <v>-15.517241379310</v>
+        <v>-11.693548387096</v>
       </c>
       <c r="M24" s="15">
-        <v>9.497206703910</v>
+        <v>2.336448598130</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D25" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>83.333333333333</v>
+        <v>112.5</v>
       </c>
       <c r="F25" s="14">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G25" s="14">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H25" s="15">
-        <v>17.647058823529</v>
+        <v>32</v>
       </c>
       <c r="I25" s="14">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="J25" s="14">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="K25" s="15">
-        <v>5.660377358490</v>
+        <v>13.157894736842</v>
       </c>
       <c r="L25" s="15">
-        <v>-15.151515151515</v>
+        <v>-11.034482758620</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-12.5</v>
+        <v>-25</v>
       </c>
       <c r="F26" s="14">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G26" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H26" s="15">
-        <v>22.5</v>
+        <v>4.878048780487</v>
       </c>
       <c r="I26" s="14">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="J26" s="14">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="K26" s="15">
-        <v>32.876712328767</v>
+        <v>23.529411764705</v>
       </c>
       <c r="L26" s="15">
-        <v>4.301075268817</v>
+        <v>5</v>
       </c>
       <c r="M26" s="15">
-        <v>64.406779661017</v>
+        <v>59.090909090909</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>4</v>
       </c>
-      <c r="E27" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F27" s="14">
-        <v>3</v>
-      </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
         <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L27" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
+        <v>3</v>
+      </c>
+      <c r="G28" s="14">
         <v>4</v>
       </c>
-      <c r="G28" s="14">
-        <v>3</v>
-      </c>
       <c r="H28" s="15">
-        <v>33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
         <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="L28" s="15">
-        <v>-27.272727272727</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>3</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-045pct.xlsx
+++ b/data/source/weekly/cs-en-us-045pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -885,7 +885,7 @@
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>6</v>
+      </c>
+      <c r="G15" s="14">
+        <v>5</v>
+      </c>
+      <c r="H15" s="15">
         <v>20</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>4</v>
-      </c>
-      <c r="G15" s="14">
-        <v>3</v>
-      </c>
-      <c r="H15" s="15">
-        <v>33.333333333333</v>
-      </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="L15" s="15">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="M15" s="15">
-        <v>80</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>23.076923076923</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J16" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K16" s="15">
-        <v>-20.930232558139</v>
+        <v>-25</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.659574468085</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="M16" s="15">
-        <v>-20.930232558139</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="N16" s="15">
-        <v>-58.536585365853</v>
+        <v>-59.550561797752</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-9.090909090909</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G17" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H17" s="15">
-        <v>-52.777777777777</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="I17" s="14">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="J17" s="14">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K17" s="15">
-        <v>-16.666666666666</v>
+        <v>-15.277777777777</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.333333333333</v>
+        <v>-3.174603174603</v>
       </c>
       <c r="M17" s="15">
-        <v>71.875</v>
+        <v>64.864864864864</v>
       </c>
       <c r="N17" s="15">
-        <v>14.583333333333</v>
+        <v>12.962962962963</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="I18" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K18" s="15">
-        <v>-51.351351351351</v>
+        <v>-51.282051282051</v>
       </c>
       <c r="L18" s="15">
-        <v>-14.285714285714</v>
+        <v>-24</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.705882352941</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.679245283018</v>
+        <v>-88.690476190476</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,13 +1057,13 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>66.666666666666</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F19" s="14">
         <v>53</v>
@@ -1075,22 +1075,22 @@
         <v>23.255813953488</v>
       </c>
       <c r="I19" s="14">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="J19" s="14">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="K19" s="15">
-        <v>30.851063829787</v>
+        <v>22.429906542056</v>
       </c>
       <c r="L19" s="15">
-        <v>-0.806451612903</v>
+        <v>-1.503759398496</v>
       </c>
       <c r="M19" s="15">
-        <v>80.882352941176</v>
+        <v>74.666666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>51.851851851851</v>
+        <v>55.952380952380</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
         <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G20" s="14">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H20" s="15">
-        <v>28.125</v>
+        <v>42.307692307692</v>
       </c>
       <c r="I20" s="14">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="J20" s="14">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K20" s="15">
-        <v>-4.444444444444</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>14.666666666666</v>
+        <v>9.302325581395</v>
       </c>
       <c r="M20" s="15">
-        <v>218.518518518519</v>
+        <v>224.137931034483</v>
       </c>
       <c r="N20" s="15">
-        <v>-75.072463768115</v>
+        <v>-74.798927613941</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D21" s="17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E21" s="18">
-        <v>32.352941176470</v>
+        <v>-15.625</v>
       </c>
       <c r="F21" s="17">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G21" s="17">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.729729729729</v>
+        <v>-4.895104895104</v>
       </c>
       <c r="I21" s="17">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="J21" s="17">
-        <v>337</v>
+        <v>369</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.264094955489</v>
+        <v>-4.336043360433</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.102102102102</v>
+        <v>-3.021978021978</v>
       </c>
       <c r="M21" s="18">
-        <v>44.247787610619</v>
+        <v>41.2</v>
       </c>
       <c r="N21" s="18">
-        <v>-54.722222222222</v>
+        <v>-54.451612903225</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1188,29 +1188,29 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F22" s="14">
+        <v>1</v>
+      </c>
+      <c r="G22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-100</v>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
+        <v>50</v>
+      </c>
+      <c r="L22" s="15">
+        <v>50</v>
+      </c>
+      <c r="M22" s="15">
         <v>0</v>
-      </c>
-      <c r="L22" s="15">
-        <v>0</v>
-      </c>
-      <c r="M22" s="15">
-        <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,32 +1220,32 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>1</v>
       </c>
       <c r="G23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
         <v>3</v>
       </c>
       <c r="J23" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K23" s="15">
-        <v>-70</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="L23" s="15">
         <v>-75</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E24" s="15">
-        <v>60</v>
+        <v>10.344827586206</v>
       </c>
       <c r="F24" s="14">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="G24" s="14">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H24" s="15">
-        <v>6.976744186046</v>
+        <v>4.901960784313</v>
       </c>
       <c r="I24" s="14">
-        <v>219</v>
+        <v>251</v>
       </c>
       <c r="J24" s="14">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="K24" s="15">
-        <v>5.797101449275</v>
+        <v>6.355932203389</v>
       </c>
       <c r="L24" s="15">
-        <v>-11.693548387096</v>
+        <v>-9.386281588447</v>
       </c>
       <c r="M24" s="15">
-        <v>2.336448598130</v>
+        <v>5.462184873949</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E25" s="15">
-        <v>112.5</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="F25" s="14">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G25" s="14">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H25" s="15">
-        <v>32</v>
+        <v>13.846153846153</v>
       </c>
       <c r="I25" s="14">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="J25" s="14">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="K25" s="15">
-        <v>13.157894736842</v>
+        <v>8.823529411764</v>
       </c>
       <c r="L25" s="15">
-        <v>-11.034482758620</v>
+        <v>-5.732484076433</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>13</v>
+      </c>
+      <c r="D26" s="14">
         <v>9</v>
       </c>
-      <c r="D26" s="14">
-        <v>12</v>
-      </c>
       <c r="E26" s="15">
-        <v>-25</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F26" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G26" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>4.878048780487</v>
+        <v>-2.380952380952</v>
       </c>
       <c r="I26" s="14">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="J26" s="14">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="K26" s="15">
-        <v>23.529411764705</v>
+        <v>25.531914893617</v>
       </c>
       <c r="L26" s="15">
-        <v>5</v>
+        <v>4.424778761061</v>
       </c>
       <c r="M26" s="15">
-        <v>59.090909090909</v>
+        <v>66.197183098591</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>3</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>28.571428571428</v>
+        <v>10</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>83.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,7 +1429,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
@@ -1438,22 +1438,22 @@
         <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="I28" s="14">
         <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>-50</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="L28" s="15">
-        <v>-38.461538461538</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,40 +1475,40 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,32 +1516,32 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-045pct.xlsx
+++ b/data/source/weekly/cs-en-us-045pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -893,13 +893,13 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>6</v>
@@ -911,22 +911,22 @@
         <v>20</v>
       </c>
       <c r="I15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J15" s="14">
         <v>8</v>
       </c>
       <c r="K15" s="15">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>83.333333333333</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-60</v>
+        <v>-75</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
         <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>-26.666666666666</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J16" s="14">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K16" s="15">
-        <v>-25</v>
+        <v>-28.846153846153</v>
       </c>
       <c r="L16" s="15">
-        <v>-29.411764705882</v>
+        <v>-33.928571428571</v>
       </c>
       <c r="M16" s="15">
-        <v>-21.739130434782</v>
+        <v>-24.489795918367</v>
       </c>
       <c r="N16" s="15">
-        <v>-59.550561797752</v>
+        <v>-62.244897959183</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-16.666666666666</v>
+        <v>125</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G17" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H17" s="15">
-        <v>-35.294117647058</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="I17" s="14">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="J17" s="14">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K17" s="15">
-        <v>-15.277777777777</v>
+        <v>-6.578947368421</v>
       </c>
       <c r="L17" s="15">
-        <v>-3.174603174603</v>
+        <v>4.411764705882</v>
       </c>
       <c r="M17" s="15">
-        <v>64.864864864864</v>
+        <v>77.5</v>
       </c>
       <c r="N17" s="15">
-        <v>12.962962962963</v>
+        <v>29.090909090909</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>-63.157894736842</v>
+        <v>-81.25</v>
       </c>
       <c r="I18" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K18" s="15">
-        <v>-51.282051282051</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="L18" s="15">
-        <v>-24</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="M18" s="15">
-        <v>-66.666666666666</v>
+        <v>-68.253968253968</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.690476190476</v>
+        <v>-89.247311827957</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="E19" s="15">
-        <v>-30.769230769230</v>
+        <v>-58.064516129032</v>
       </c>
       <c r="F19" s="14">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G19" s="14">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="H19" s="15">
-        <v>23.255813953488</v>
+        <v>-16.393442622950</v>
       </c>
       <c r="I19" s="14">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="J19" s="14">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="K19" s="15">
-        <v>22.429906542056</v>
+        <v>4.347826086956</v>
       </c>
       <c r="L19" s="15">
-        <v>-1.503759398496</v>
+        <v>-1.369863013698</v>
       </c>
       <c r="M19" s="15">
-        <v>74.666666666666</v>
+        <v>77.777777777777</v>
       </c>
       <c r="N19" s="15">
-        <v>55.952380952380</v>
+        <v>54.838709677419</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F20" s="14">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G20" s="14">
         <v>26</v>
       </c>
       <c r="H20" s="15">
-        <v>42.307692307692</v>
+        <v>23.076923076923</v>
       </c>
       <c r="I20" s="14">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="J20" s="14">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>3.030303030303</v>
       </c>
       <c r="L20" s="15">
-        <v>9.302325581395</v>
+        <v>8.510638297872</v>
       </c>
       <c r="M20" s="15">
-        <v>224.137931034483</v>
+        <v>229.032258064516</v>
       </c>
       <c r="N20" s="15">
-        <v>-74.798927613941</v>
+        <v>-75.539568345323</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D21" s="17">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E21" s="18">
-        <v>-15.625</v>
+        <v>-31.914893617021</v>
       </c>
       <c r="F21" s="17">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="G21" s="17">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.895104895104</v>
+        <v>-20.253164556962</v>
       </c>
       <c r="I21" s="17">
-        <v>353</v>
+        <v>387</v>
       </c>
       <c r="J21" s="17">
-        <v>369</v>
+        <v>416</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.336043360433</v>
+        <v>-6.971153846153</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.021978021978</v>
+        <v>-3.25</v>
       </c>
       <c r="M21" s="18">
-        <v>41.2</v>
+        <v>43.333333333333</v>
       </c>
       <c r="N21" s="18">
-        <v>-54.451612903225</v>
+        <v>-54.789719626168</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1223,20 +1223,20 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>1</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
         <v>3</v>
@@ -1248,10 +1248,10 @@
         <v>-72.727272727272</v>
       </c>
       <c r="L23" s="15">
-        <v>-75</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="M23" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D24" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>10.344827586206</v>
+        <v>10.714285714285</v>
       </c>
       <c r="F24" s="14">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="G24" s="14">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="H24" s="15">
-        <v>4.901960784313</v>
+        <v>26.595744680851</v>
       </c>
       <c r="I24" s="14">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="J24" s="14">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="K24" s="15">
-        <v>6.355932203389</v>
+        <v>7.196969696969</v>
       </c>
       <c r="L24" s="15">
-        <v>-9.386281588447</v>
+        <v>-8.414239482200</v>
       </c>
       <c r="M24" s="15">
-        <v>5.462184873949</v>
+        <v>8.846153846153</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>20</v>
+      </c>
+      <c r="D25" s="14">
         <v>19</v>
       </c>
-      <c r="D25" s="14">
-        <v>22</v>
-      </c>
       <c r="E25" s="15">
-        <v>-13.636363636363</v>
+        <v>5.263157894736</v>
       </c>
       <c r="F25" s="14">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G25" s="14">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H25" s="15">
-        <v>13.846153846153</v>
+        <v>31.147540983606</v>
       </c>
       <c r="I25" s="14">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="J25" s="14">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="K25" s="15">
-        <v>8.823529411764</v>
+        <v>9.677419354838</v>
       </c>
       <c r="L25" s="15">
-        <v>-5.732484076433</v>
+        <v>-1.162790697674</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>9</v>
+      </c>
+      <c r="D26" s="14">
         <v>13</v>
       </c>
-      <c r="D26" s="14">
-        <v>9</v>
-      </c>
       <c r="E26" s="15">
-        <v>44.444444444444</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F26" s="14">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G26" s="14">
         <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>-2.380952380952</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I26" s="14">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J26" s="14">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="K26" s="15">
-        <v>25.531914893617</v>
+        <v>16.822429906542</v>
       </c>
       <c r="L26" s="15">
-        <v>4.424778761061</v>
+        <v>1.626016260162</v>
       </c>
       <c r="M26" s="15">
-        <v>66.197183098591</v>
+        <v>54.320987654321</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="14">
-        <v>3</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-33.333333333333</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G27" s="14">
         <v>7</v>
       </c>
       <c r="H27" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J27" s="14">
         <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="L27" s="15">
-        <v>83.333333333333</v>
+        <v>62.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,25 +1435,25 @@
         <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-40</v>
+        <v>-75</v>
       </c>
       <c r="I28" s="14">
         <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>-52.941176470588</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L28" s="15">
-        <v>-42.857142857142</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>0</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1519,11 +1519,11 @@
       <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>0</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>

--- a/data/source/weekly/cs-en-us-045pct.xlsx
+++ b/data/source/weekly/cs-en-us-045pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -885,7 +885,7 @@
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,7 +893,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,28 +905,28 @@
         <v>6</v>
       </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="I15" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J15" s="14">
         <v>8</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>87.5</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>114.285714285714</v>
       </c>
       <c r="N15" s="15">
-        <v>140</v>
+        <v>114.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
         <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H16" s="15">
-        <v>-53.333333333333</v>
+        <v>-69.565217391304</v>
       </c>
       <c r="I16" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J16" s="14">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="K16" s="15">
-        <v>-28.846153846153</v>
+        <v>-34.426229508196</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.928571428571</v>
+        <v>-37.5</v>
       </c>
       <c r="M16" s="15">
-        <v>-24.489795918367</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N16" s="15">
-        <v>-62.244897959183</v>
+        <v>-63.302752293578</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G17" s="14">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H17" s="15">
-        <v>-22.857142857142</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I17" s="14">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J17" s="14">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K17" s="15">
-        <v>-6.578947368421</v>
+        <v>-6.024096385542</v>
       </c>
       <c r="L17" s="15">
-        <v>4.411764705882</v>
+        <v>-1.265822784810</v>
       </c>
       <c r="M17" s="15">
-        <v>77.5</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N17" s="15">
-        <v>29.090909090909</v>
+        <v>32.203389830508</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-81.25</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I18" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J18" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K18" s="15">
-        <v>-52.380952380952</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="L18" s="15">
-        <v>-31.034482758620</v>
+        <v>-31.25</v>
       </c>
       <c r="M18" s="15">
-        <v>-68.253968253968</v>
+        <v>-66.153846153846</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.247311827957</v>
+        <v>-89.268292682926</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D19" s="14">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>-58.064516129032</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G19" s="14">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H19" s="15">
-        <v>-16.393442622950</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="I19" s="14">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="J19" s="14">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="K19" s="15">
-        <v>4.347826086956</v>
+        <v>11.486486486486</v>
       </c>
       <c r="L19" s="15">
-        <v>-1.369863013698</v>
+        <v>1.226993865030</v>
       </c>
       <c r="M19" s="15">
-        <v>77.777777777777</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>54.838709677419</v>
+        <v>66.666666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E20" s="15">
-        <v>60</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F20" s="14">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G20" s="14">
         <v>26</v>
       </c>
       <c r="H20" s="15">
-        <v>23.076923076923</v>
+        <v>53.846153846153</v>
       </c>
       <c r="I20" s="14">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="J20" s="14">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="K20" s="15">
-        <v>3.030303030303</v>
+        <v>1.785714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>8.510638297872</v>
+        <v>16.326530612244</v>
       </c>
       <c r="M20" s="15">
-        <v>229.032258064516</v>
+        <v>200</v>
       </c>
       <c r="N20" s="15">
-        <v>-75.539568345323</v>
+        <v>-74.324324324324</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D21" s="17">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E21" s="18">
-        <v>-31.914893617021</v>
+        <v>4.651162790697</v>
       </c>
       <c r="F21" s="17">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="G21" s="17">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H21" s="18">
-        <v>-20.253164556962</v>
+        <v>-2.564102564102</v>
       </c>
       <c r="I21" s="17">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="J21" s="17">
-        <v>416</v>
+        <v>459</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.971153846153</v>
+        <v>-5.228758169934</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.25</v>
+        <v>-1.805869074492</v>
       </c>
       <c r="M21" s="18">
-        <v>43.333333333333</v>
+        <v>46.464646464646</v>
       </c>
       <c r="N21" s="18">
-        <v>-54.789719626168</v>
+        <v>-53.023758099352</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J23" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K23" s="15">
-        <v>-72.727272727272</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>-76.923076923076</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="M23" s="15">
-        <v>-57.142857142857</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>10.714285714285</v>
+        <v>51.851851851851</v>
       </c>
       <c r="F24" s="14">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="G24" s="14">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H24" s="15">
-        <v>26.595744680851</v>
+        <v>29.292929292929</v>
       </c>
       <c r="I24" s="14">
-        <v>283</v>
+        <v>322</v>
       </c>
       <c r="J24" s="14">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="K24" s="15">
-        <v>7.196969696969</v>
+        <v>10.652920962199</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.414239482200</v>
+        <v>-2.424242424242</v>
       </c>
       <c r="M24" s="15">
-        <v>8.846153846153</v>
+        <v>7.692307692307</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>5.263157894736</v>
+        <v>181.818181818182</v>
       </c>
       <c r="F25" s="14">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G25" s="14">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H25" s="15">
-        <v>31.147540983606</v>
+        <v>53.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>170</v>
+        <v>203</v>
       </c>
       <c r="J25" s="14">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="K25" s="15">
-        <v>9.677419354838</v>
+        <v>22.289156626506</v>
       </c>
       <c r="L25" s="15">
-        <v>-1.162790697674</v>
+        <v>5.181347150259</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-30.769230769230</v>
+        <v>-37.5</v>
       </c>
       <c r="F26" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G26" s="14">
         <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>-14.285714285714</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I26" s="14">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J26" s="14">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="K26" s="15">
-        <v>16.822429906542</v>
+        <v>13.043478260869</v>
       </c>
       <c r="L26" s="15">
-        <v>1.626016260162</v>
+        <v>-0.763358778625</v>
       </c>
       <c r="M26" s="15">
-        <v>54.320987654321</v>
+        <v>34.020618556701</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,22 +1397,22 @@
         <v>7</v>
       </c>
       <c r="G27" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J27" s="14">
         <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="L27" s="15">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="14">
-        <v>1</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J28" s="14">
         <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>-55.555555555555</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="L28" s="15">
-        <v>-55.555555555555</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="14">
-        <v>3</v>
-      </c>
-      <c r="H31" s="15">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-045pct.xlsx
+++ b/data/source/weekly/cs-en-us-045pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L14" s="15">
         <v>0</v>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
         <v>2</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
         <v>6</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>87.5</v>
+        <v>60</v>
       </c>
       <c r="L15" s="15">
-        <v>150</v>
+        <v>128.571428571429</v>
       </c>
       <c r="M15" s="15">
-        <v>114.285714285714</v>
+        <v>128.571428571429</v>
       </c>
       <c r="N15" s="15">
-        <v>114.285714285714</v>
+        <v>128.571428571429</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H16" s="15">
-        <v>-69.565217391304</v>
+        <v>-60</v>
       </c>
       <c r="I16" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J16" s="14">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K16" s="15">
-        <v>-34.426229508196</v>
+        <v>-31.746031746031</v>
       </c>
       <c r="L16" s="15">
-        <v>-37.5</v>
+        <v>-39.436619718309</v>
       </c>
       <c r="M16" s="15">
-        <v>-27.272727272727</v>
+        <v>-25.862068965517</v>
       </c>
       <c r="N16" s="15">
-        <v>-63.302752293578</v>
+        <v>-65.040650406504</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
+        <v>-60</v>
+      </c>
+      <c r="F17" s="14">
+        <v>27</v>
+      </c>
+      <c r="G17" s="14">
+        <v>27</v>
+      </c>
+      <c r="H17" s="15">
         <v>0</v>
       </c>
-      <c r="F17" s="14">
-        <v>32</v>
-      </c>
-      <c r="G17" s="14">
-        <v>28</v>
-      </c>
-      <c r="H17" s="15">
-        <v>14.285714285714</v>
-      </c>
       <c r="I17" s="14">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J17" s="14">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K17" s="15">
-        <v>-6.024096385542</v>
+        <v>-10.752688172043</v>
       </c>
       <c r="L17" s="15">
-        <v>-1.265822784810</v>
+        <v>0</v>
       </c>
       <c r="M17" s="15">
-        <v>85.714285714285</v>
+        <v>84.444444444444</v>
       </c>
       <c r="N17" s="15">
-        <v>32.203389830508</v>
+        <v>25.757575757575</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>2</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="14">
-        <v>4</v>
-      </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>-63.636363636363</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J18" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K18" s="15">
-        <v>-52.173913043478</v>
+        <v>-48.936170212766</v>
       </c>
       <c r="L18" s="15">
-        <v>-31.25</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M18" s="15">
-        <v>-66.153846153846</v>
+        <v>-65.217391304347</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.268292682926</v>
+        <v>-89.237668161435</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F19" s="14">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G19" s="14">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H19" s="15">
-        <v>-4.545454545454</v>
+        <v>-22.388059701492</v>
       </c>
       <c r="I19" s="14">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="J19" s="14">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="K19" s="15">
-        <v>11.486486486486</v>
+        <v>8.695652173913</v>
       </c>
       <c r="L19" s="15">
-        <v>1.226993865030</v>
+        <v>-1.129943502824</v>
       </c>
       <c r="M19" s="15">
-        <v>83.333333333333</v>
+        <v>80.412371134020</v>
       </c>
       <c r="N19" s="15">
-        <v>66.666666666666</v>
+        <v>65.094339622641</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E20" s="15">
-        <v>-7.692307692307</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F20" s="14">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G20" s="14">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H20" s="15">
-        <v>53.846153846153</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J20" s="14">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="K20" s="15">
-        <v>1.785714285714</v>
+        <v>-3.252032520325</v>
       </c>
       <c r="L20" s="15">
-        <v>16.326530612244</v>
+        <v>13.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>200</v>
+        <v>190.243902439024</v>
       </c>
       <c r="N20" s="15">
-        <v>-74.324324324324</v>
+        <v>-75.813008130081</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E21" s="18">
-        <v>4.651162790697</v>
+        <v>-40</v>
       </c>
       <c r="F21" s="17">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="G21" s="17">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.564102564102</v>
+        <v>-19.135802469135</v>
       </c>
       <c r="I21" s="17">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="J21" s="17">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.228758169934</v>
+        <v>-7.615230460921</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.805869074492</v>
+        <v>-4.554865424430</v>
       </c>
       <c r="M21" s="18">
-        <v>46.464646464646</v>
+        <v>45.425867507886</v>
       </c>
       <c r="N21" s="18">
-        <v>-53.023758099352</v>
+        <v>-54.803921568627</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L22" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
         <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>-25</v>
       </c>
       <c r="I23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K23" s="15">
-        <v>-58.333333333333</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L23" s="15">
-        <v>-64.285714285714</v>
+        <v>-60</v>
       </c>
       <c r="M23" s="15">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E24" s="15">
-        <v>51.851851851851</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="F24" s="14">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="G24" s="14">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="H24" s="15">
-        <v>29.292929292929</v>
+        <v>7.936507936507</v>
       </c>
       <c r="I24" s="14">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="J24" s="14">
-        <v>291</v>
+        <v>333</v>
       </c>
       <c r="K24" s="15">
-        <v>10.652920962199</v>
+        <v>6.006006006006</v>
       </c>
       <c r="L24" s="15">
-        <v>-2.424242424242</v>
+        <v>-2.754820936639</v>
       </c>
       <c r="M24" s="15">
-        <v>7.692307692307</v>
+        <v>8.950617283950</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E25" s="15">
-        <v>181.818181818182</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F25" s="14">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G25" s="14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H25" s="15">
-        <v>53.333333333333</v>
+        <v>21.25</v>
       </c>
       <c r="I25" s="14">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="J25" s="14">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="K25" s="15">
-        <v>22.289156626506</v>
+        <v>15.979381443299</v>
       </c>
       <c r="L25" s="15">
-        <v>5.181347150259</v>
+        <v>6.635071090047</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>-37.5</v>
+        <v>23.076923076923</v>
       </c>
       <c r="F26" s="14">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G26" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>-19.047619047619</v>
+        <v>-2.325581395348</v>
       </c>
       <c r="I26" s="14">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="J26" s="14">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="K26" s="15">
-        <v>13.043478260869</v>
+        <v>14.0625</v>
       </c>
       <c r="L26" s="15">
-        <v>-0.763358778625</v>
+        <v>7.352941176470</v>
       </c>
       <c r="M26" s="15">
-        <v>34.020618556701</v>
+        <v>41.747572815534</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
         <v>7</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>133.333333333333</v>
+        <v>40</v>
       </c>
       <c r="I27" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J27" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>60</v>
+        <v>41.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>100</v>
+        <v>88.888888888888</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1438,7 +1438,7 @@
         <v>20</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
         <v>-100</v>
@@ -1496,8 +1496,8 @@
       <c r="L29" s="15">
         <v>100</v>
       </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
+      <c r="M29" s="15">
+        <v>100</v>
       </c>
       <c r="N29" s="15">
         <v>-60</v>
@@ -1537,8 +1537,8 @@
       <c r="L30" s="15">
         <v>100</v>
       </c>
-      <c r="M30" s="13" t="s">
-        <v>21</v>
+      <c r="M30" s="15">
+        <v>100</v>
       </c>
       <c r="N30" s="15">
         <v>-60</v>

--- a/data/source/weekly/cs-en-us-045pct.xlsx
+++ b/data/source/weekly/cs-en-us-045pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>4</v>
+      </c>
+      <c r="G15" s="14">
         <v>2</v>
       </c>
-      <c r="E15" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F15" s="14">
-        <v>6</v>
-      </c>
-      <c r="G15" s="14">
-        <v>4</v>
-      </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>16</v>
@@ -920,7 +920,7 @@
         <v>60</v>
       </c>
       <c r="L15" s="15">
-        <v>128.571428571429</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
         <v>128.571428571429</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>2</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H16" s="15">
-        <v>-60</v>
+        <v>-68.421052631578</v>
       </c>
       <c r="I16" s="14">
         <v>43</v>
       </c>
       <c r="J16" s="14">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K16" s="15">
-        <v>-31.746031746031</v>
+        <v>-35.820895522388</v>
       </c>
       <c r="L16" s="15">
-        <v>-39.436619718309</v>
+        <v>-41.095890410958</v>
       </c>
       <c r="M16" s="15">
-        <v>-25.862068965517</v>
+        <v>-29.508196721311</v>
       </c>
       <c r="N16" s="15">
-        <v>-65.040650406504</v>
+        <v>-67.175572519084</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>10</v>
+      </c>
+      <c r="D17" s="14">
         <v>4</v>
       </c>
-      <c r="D17" s="14">
-        <v>10</v>
-      </c>
       <c r="E17" s="15">
-        <v>-60</v>
+        <v>150</v>
       </c>
       <c r="F17" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I17" s="14">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J17" s="14">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.752688172043</v>
+        <v>-4.123711340206</v>
       </c>
       <c r="L17" s="15">
-        <v>0</v>
+        <v>6.896551724137</v>
       </c>
       <c r="M17" s="15">
-        <v>84.444444444444</v>
+        <v>86</v>
       </c>
       <c r="N17" s="15">
-        <v>25.757575757575</v>
+        <v>40.909090909090</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,13 +1016,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>5</v>
@@ -1034,22 +1034,22 @@
         <v>-50</v>
       </c>
       <c r="I18" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J18" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K18" s="15">
-        <v>-48.936170212766</v>
+        <v>-48.979591836734</v>
       </c>
       <c r="L18" s="15">
-        <v>-38.461538461538</v>
+        <v>-43.181818181818</v>
       </c>
       <c r="M18" s="15">
-        <v>-65.217391304347</v>
+        <v>-64.788732394366</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.237668161435</v>
+        <v>-89.583333333333</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E19" s="15">
-        <v>-23.076923076923</v>
+        <v>-59.090909090909</v>
       </c>
       <c r="F19" s="14">
         <v>52</v>
       </c>
       <c r="G19" s="14">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="H19" s="15">
-        <v>-22.388059701492</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I19" s="14">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J19" s="14">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="K19" s="15">
-        <v>8.695652173913</v>
+        <v>0</v>
       </c>
       <c r="L19" s="15">
-        <v>-1.129943502824</v>
+        <v>-1.081081081081</v>
       </c>
       <c r="M19" s="15">
-        <v>80.412371134020</v>
+        <v>74.285714285714</v>
       </c>
       <c r="N19" s="15">
-        <v>65.094339622641</v>
+        <v>66.363636363636</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D20" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E20" s="15">
-        <v>-54.545454545454</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G20" s="14">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-11.904761904761</v>
       </c>
       <c r="I20" s="14">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="J20" s="14">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="K20" s="15">
-        <v>-3.252032520325</v>
+        <v>-3.676470588235</v>
       </c>
       <c r="L20" s="15">
-        <v>13.333333333333</v>
+        <v>20.183486238532</v>
       </c>
       <c r="M20" s="15">
-        <v>190.243902439024</v>
+        <v>204.651162790698</v>
       </c>
       <c r="N20" s="15">
-        <v>-75.813008130081</v>
+        <v>-75.785582255083</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E21" s="18">
-        <v>-40</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G21" s="17">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.135802469135</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="I21" s="17">
-        <v>461</v>
+        <v>492</v>
       </c>
       <c r="J21" s="17">
-        <v>499</v>
+        <v>544</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.615230460921</v>
+        <v>-9.558823529411</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.554865424430</v>
+        <v>-2.958579881656</v>
       </c>
       <c r="M21" s="18">
-        <v>45.425867507886</v>
+        <v>45.994065281899</v>
       </c>
       <c r="N21" s="18">
-        <v>-54.803921568627</v>
+        <v>-55.191256830601</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1210,7 +1210,7 @@
         <v>66.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
         <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K23" s="15">
-        <v>-57.142857142857</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>-60</v>
+        <v>-56.25</v>
       </c>
       <c r="M23" s="15">
-        <v>-25</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>-23.809523809523</v>
+        <v>13.636363636363</v>
       </c>
       <c r="F24" s="14">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="G24" s="14">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="H24" s="15">
-        <v>7.936507936507</v>
+        <v>6.722689075630</v>
       </c>
       <c r="I24" s="14">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="J24" s="14">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="K24" s="15">
-        <v>6.006006006006</v>
+        <v>6.197183098591</v>
       </c>
       <c r="L24" s="15">
-        <v>-2.754820936639</v>
+        <v>-4.314720812182</v>
       </c>
       <c r="M24" s="15">
-        <v>8.950617283950</v>
+        <v>8.959537572254</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>-21.428571428571</v>
+        <v>-12.5</v>
       </c>
       <c r="F25" s="14">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="G25" s="14">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H25" s="15">
-        <v>21.25</v>
+        <v>20.270270270270</v>
       </c>
       <c r="I25" s="14">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="J25" s="14">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="K25" s="15">
-        <v>15.979381443299</v>
+        <v>13.809523809523</v>
       </c>
       <c r="L25" s="15">
-        <v>6.635071090047</v>
+        <v>6.222222222222</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>23.076923076923</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
+        <v>38</v>
+      </c>
+      <c r="G26" s="14">
         <v>42</v>
       </c>
-      <c r="G26" s="14">
-        <v>43</v>
-      </c>
       <c r="H26" s="15">
-        <v>-2.325581395348</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I26" s="14">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="J26" s="14">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="K26" s="15">
-        <v>14.0625</v>
+        <v>13.235294117647</v>
       </c>
       <c r="L26" s="15">
-        <v>7.352941176470</v>
+        <v>0.653594771241</v>
       </c>
       <c r="M26" s="15">
-        <v>41.747572815534</v>
+        <v>36.283185840708</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>5</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="E27" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F27" s="14">
-        <v>7</v>
-      </c>
-      <c r="G27" s="14">
-        <v>5</v>
-      </c>
       <c r="H27" s="15">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="I27" s="14">
         <v>17</v>
@@ -1412,7 +1412,7 @@
         <v>41.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>88.888888888888</v>
+        <v>70</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,11 +1428,11 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="13" t="s">
         <v>20</v>
@@ -1447,13 +1447,13 @@
         <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>-61.111111111111</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="L28" s="15">
-        <v>-63.157894736842</v>
+        <v>-68.181818181818</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-045pct.xlsx
+++ b/data/source/weekly/cs-en-us-045pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -873,10 +873,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
         <v>0</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -911,63 +911,63 @@
         <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J15" s="14">
         <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>112.5</v>
       </c>
       <c r="M15" s="15">
-        <v>128.571428571429</v>
+        <v>142.857142857143</v>
       </c>
       <c r="N15" s="15">
-        <v>128.571428571429</v>
+        <v>142.857142857143</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>3</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
         <v>19</v>
       </c>
       <c r="H16" s="15">
-        <v>-68.421052631578</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="I16" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J16" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K16" s="15">
-        <v>-35.820895522388</v>
+        <v>-33.802816901408</v>
       </c>
       <c r="L16" s="15">
-        <v>-41.095890410958</v>
+        <v>-38.157894736842</v>
       </c>
       <c r="M16" s="15">
-        <v>-29.508196721311</v>
+        <v>-27.692307692307</v>
       </c>
       <c r="N16" s="15">
-        <v>-67.175572519084</v>
+        <v>-66.428571428571</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>8</v>
+      </c>
+      <c r="D17" s="14">
         <v>10</v>
       </c>
-      <c r="D17" s="14">
-        <v>4</v>
-      </c>
       <c r="E17" s="15">
-        <v>150</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="14">
+        <v>30</v>
+      </c>
+      <c r="G17" s="14">
         <v>31</v>
       </c>
-      <c r="G17" s="14">
-        <v>25</v>
-      </c>
       <c r="H17" s="15">
-        <v>24</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="I17" s="14">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J17" s="14">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.123711340206</v>
+        <v>-3.738317757009</v>
       </c>
       <c r="L17" s="15">
-        <v>6.896551724137</v>
+        <v>5.102040816326</v>
       </c>
       <c r="M17" s="15">
-        <v>86</v>
+        <v>83.928571428571</v>
       </c>
       <c r="N17" s="15">
-        <v>40.909090909090</v>
+        <v>51.470588235294</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
         <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J18" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K18" s="15">
-        <v>-48.979591836734</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="L18" s="15">
-        <v>-43.181818181818</v>
+        <v>-37.5</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.788732394366</v>
+        <v>-60</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.583333333333</v>
+        <v>-88.721804511278</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>-59.090909090909</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="F19" s="14">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G19" s="14">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="H19" s="15">
-        <v>-31.578947368421</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="I19" s="14">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="J19" s="14">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="K19" s="15">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L19" s="15">
-        <v>-1.081081081081</v>
+        <v>0.523560209424</v>
       </c>
       <c r="M19" s="15">
-        <v>74.285714285714</v>
+        <v>74.545454545454</v>
       </c>
       <c r="N19" s="15">
-        <v>66.363636363636</v>
+        <v>58.677685950413</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-68.75</v>
       </c>
       <c r="F20" s="14">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G20" s="14">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H20" s="15">
-        <v>-11.904761904761</v>
+        <v>-35.849056603773</v>
       </c>
       <c r="I20" s="14">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="J20" s="14">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="K20" s="15">
-        <v>-3.676470588235</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="L20" s="15">
-        <v>20.183486238532</v>
+        <v>16.239316239316</v>
       </c>
       <c r="M20" s="15">
-        <v>204.651162790698</v>
+        <v>202.222222222222</v>
       </c>
       <c r="N20" s="15">
-        <v>-75.785582255083</v>
+        <v>-76.306620209059</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E21" s="18">
-        <v>-26.666666666666</v>
+        <v>-39.215686274509</v>
       </c>
       <c r="F21" s="17">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G21" s="17">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.857142857142</v>
+        <v>-25.139664804469</v>
       </c>
       <c r="I21" s="17">
-        <v>492</v>
+        <v>526</v>
       </c>
       <c r="J21" s="17">
-        <v>544</v>
+        <v>595</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.558823529411</v>
+        <v>-11.596638655462</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.958579881656</v>
+        <v>-2.411873840445</v>
       </c>
       <c r="M21" s="18">
-        <v>45.994065281899</v>
+        <v>46.927374301676</v>
       </c>
       <c r="N21" s="18">
-        <v>-55.191256830601</v>
+        <v>-55.385920271416</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L22" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I23" s="14">
         <v>7</v>
       </c>
       <c r="J23" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K23" s="15">
-        <v>-53.333333333333</v>
+        <v>-65</v>
       </c>
       <c r="L23" s="15">
-        <v>-56.25</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="M23" s="15">
         <v>-22.222222222222</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>13.636363636363</v>
+        <v>21.428571428571</v>
       </c>
       <c r="F24" s="14">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G24" s="14">
         <v>119</v>
       </c>
       <c r="H24" s="15">
-        <v>6.722689075630</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I24" s="14">
-        <v>377</v>
+        <v>412</v>
       </c>
       <c r="J24" s="14">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="K24" s="15">
-        <v>6.197183098591</v>
+        <v>7.571801566579</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.314720812182</v>
+        <v>-3.058823529411</v>
       </c>
       <c r="M24" s="15">
-        <v>8.959537572254</v>
+        <v>12.568306010929</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E25" s="15">
-        <v>-12.5</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F25" s="14">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G25" s="14">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H25" s="15">
-        <v>20.270270270270</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I25" s="14">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="J25" s="14">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="K25" s="15">
-        <v>13.809523809523</v>
+        <v>12.068965517241</v>
       </c>
       <c r="L25" s="15">
-        <v>6.222222222222</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
         <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G26" s="14">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H26" s="15">
-        <v>-9.523809523809</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="J26" s="14">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="K26" s="15">
-        <v>13.235294117647</v>
+        <v>10.810810810810</v>
       </c>
       <c r="L26" s="15">
-        <v>0.653594771241</v>
+        <v>-2.958579881656</v>
       </c>
       <c r="M26" s="15">
-        <v>36.283185840708</v>
+        <v>42.608695652173</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J27" s="14">
         <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>41.666666666666</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,17 +1428,17 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="14">
         <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" s="14">
-        <v>2</v>
       </c>
       <c r="H28" s="15">
         <v>-100</v>
@@ -1453,7 +1453,7 @@
         <v>-63.157894736842</v>
       </c>
       <c r="L28" s="15">
-        <v>-68.181818181818</v>
+        <v>-72</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>2</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>2</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L29" s="15">
         <v>100</v>
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>2</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>2</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="15">
         <v>100</v>

--- a/data/source/weekly/cs-en-us-045pct.xlsx
+++ b/data/source/weekly/cs-en-us-045pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15" s="14">
         <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="L15" s="15">
-        <v>112.5</v>
+        <v>125</v>
       </c>
       <c r="M15" s="15">
-        <v>142.857142857143</v>
+        <v>157.142857142857</v>
       </c>
       <c r="N15" s="15">
-        <v>142.857142857143</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>-57.894736842105</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J16" s="14">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.802816901408</v>
+        <v>-34.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-38.157894736842</v>
+        <v>-39.506172839506</v>
       </c>
       <c r="M16" s="15">
-        <v>-27.692307692307</v>
+        <v>-30.985915492957</v>
       </c>
       <c r="N16" s="15">
-        <v>-66.428571428571</v>
+        <v>-66.206896551724</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
+        <v>26</v>
+      </c>
+      <c r="G17" s="14">
         <v>30</v>
       </c>
-      <c r="G17" s="14">
-        <v>31</v>
-      </c>
       <c r="H17" s="15">
-        <v>-3.225806451612</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="J17" s="14">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.738317757009</v>
+        <v>-5.309734513274</v>
       </c>
       <c r="L17" s="15">
-        <v>5.102040816326</v>
+        <v>1.904761904761</v>
       </c>
       <c r="M17" s="15">
-        <v>83.928571428571</v>
+        <v>84.482758620689</v>
       </c>
       <c r="N17" s="15">
-        <v>51.470588235294</v>
+        <v>50.704225352112</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
         <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I18" s="14">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="J18" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K18" s="15">
-        <v>-42.307692307692</v>
+        <v>-33.928571428571</v>
       </c>
       <c r="L18" s="15">
-        <v>-37.5</v>
+        <v>-24.489795918367</v>
       </c>
       <c r="M18" s="15">
-        <v>-60</v>
+        <v>-53.164556962025</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.721804511278</v>
+        <v>-86.594202898550</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-52.941176470588</v>
+        <v>15.384615384615</v>
       </c>
       <c r="F19" s="14">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G19" s="14">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H19" s="15">
-        <v>-22.580645161290</v>
+        <v>-32.307692307692</v>
       </c>
       <c r="I19" s="14">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="J19" s="14">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="K19" s="15">
-        <v>-4</v>
+        <v>-1.408450704225</v>
       </c>
       <c r="L19" s="15">
-        <v>0.523560209424</v>
+        <v>3.448275862068</v>
       </c>
       <c r="M19" s="15">
-        <v>74.545454545454</v>
+        <v>70.731707317073</v>
       </c>
       <c r="N19" s="15">
-        <v>58.677685950413</v>
+        <v>64.0625</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>4</v>
+      </c>
+      <c r="D20" s="14">
         <v>5</v>
       </c>
-      <c r="D20" s="14">
-        <v>16</v>
-      </c>
       <c r="E20" s="15">
-        <v>-68.75</v>
+        <v>-20</v>
       </c>
       <c r="F20" s="14">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G20" s="14">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H20" s="15">
-        <v>-35.849056603773</v>
+        <v>-40</v>
       </c>
       <c r="I20" s="14">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="J20" s="14">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="K20" s="15">
-        <v>-10.526315789473</v>
+        <v>-10.828025477707</v>
       </c>
       <c r="L20" s="15">
-        <v>16.239316239316</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M20" s="15">
-        <v>202.222222222222</v>
+        <v>197.872340425532</v>
       </c>
       <c r="N20" s="15">
-        <v>-76.306620209059</v>
+        <v>-76.973684210526</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E21" s="18">
-        <v>-39.215686274509</v>
+        <v>3.125</v>
       </c>
       <c r="F21" s="17">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="G21" s="17">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.139664804469</v>
+        <v>-26.785714285714</v>
       </c>
       <c r="I21" s="17">
-        <v>526</v>
+        <v>562</v>
       </c>
       <c r="J21" s="17">
-        <v>595</v>
+        <v>627</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.596638655462</v>
+        <v>-10.366826156299</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.411873840445</v>
+        <v>-1.919720767888</v>
       </c>
       <c r="M21" s="18">
-        <v>46.927374301676</v>
+        <v>45.974025974026</v>
       </c>
       <c r="N21" s="18">
-        <v>-55.385920271416</v>
+        <v>-54.640839386602</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M22" s="15">
-        <v>20</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
         <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H23" s="15">
-        <v>-55.555555555555</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="I23" s="14">
         <v>7</v>
       </c>
       <c r="J23" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K23" s="15">
+        <v>-69.565217391304</v>
+      </c>
+      <c r="L23" s="15">
         <v>-65</v>
       </c>
-      <c r="L23" s="15">
-        <v>-61.111111111111</v>
-      </c>
       <c r="M23" s="15">
-        <v>-22.222222222222</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="E24" s="15">
-        <v>21.428571428571</v>
+        <v>-51.724137931034</v>
       </c>
       <c r="F24" s="14">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="G24" s="14">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="H24" s="15">
-        <v>11.764705882352</v>
+        <v>-20</v>
       </c>
       <c r="I24" s="14">
-        <v>412</v>
+        <v>440</v>
       </c>
       <c r="J24" s="14">
-        <v>383</v>
+        <v>441</v>
       </c>
       <c r="K24" s="15">
-        <v>7.571801566579</v>
+        <v>-0.226757369614</v>
       </c>
       <c r="L24" s="15">
-        <v>-3.058823529411</v>
+        <v>-3.508771929824</v>
       </c>
       <c r="M24" s="15">
-        <v>12.568306010929</v>
+        <v>10.275689223057</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D25" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E25" s="15">
-        <v>-9.090909090909</v>
+        <v>-32</v>
       </c>
       <c r="F25" s="14">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G25" s="14">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="H25" s="15">
-        <v>14.285714285714</v>
+        <v>-17.582417582417</v>
       </c>
       <c r="I25" s="14">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="J25" s="14">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="K25" s="15">
-        <v>12.068965517241</v>
+        <v>8.171206225680</v>
       </c>
       <c r="L25" s="15">
-        <v>8.333333333333</v>
+        <v>5.703422053231</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="F26" s="14">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G26" s="14">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>34.210526315789</v>
       </c>
       <c r="I26" s="14">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="J26" s="14">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="K26" s="15">
-        <v>10.810810810810</v>
+        <v>16.993464052287</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.958579881656</v>
+        <v>0.561797752808</v>
       </c>
       <c r="M26" s="15">
-        <v>42.608695652173</v>
+        <v>49.166666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,7 +1385,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1403,16 +1403,16 @@
         <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J27" s="14">
         <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>2</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1434,26 +1434,26 @@
       <c r="E28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+      <c r="F28" s="14">
+        <v>2</v>
       </c>
       <c r="G28" s="14">
         <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
         <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>-63.157894736842</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="L28" s="15">
-        <v>-72</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>2</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-045pct.xlsx
+++ b/data/source/weekly/cs-en-us-045pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -864,7 +864,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -879,7 +879,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>3</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
+      <c r="G15" s="14">
         <v>3</v>
       </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K15" s="15">
-        <v>80</v>
+        <v>30.769230769230</v>
       </c>
       <c r="L15" s="15">
-        <v>125</v>
+        <v>88.888888888888</v>
       </c>
       <c r="M15" s="15">
-        <v>157.142857142857</v>
+        <v>142.857142857143</v>
       </c>
       <c r="N15" s="15">
-        <v>125</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="I16" s="14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J16" s="14">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K16" s="15">
-        <v>-34.666666666666</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="L16" s="15">
-        <v>-39.506172839506</v>
+        <v>-39.759036144578</v>
       </c>
       <c r="M16" s="15">
-        <v>-30.985915492957</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-66.206896551724</v>
+        <v>-66.887417218543</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>300</v>
       </c>
       <c r="F17" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G17" s="14">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H17" s="15">
-        <v>-13.333333333333</v>
+        <v>36.363636363636</v>
       </c>
       <c r="I17" s="14">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="J17" s="14">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.309734513274</v>
+        <v>0.869565217391</v>
       </c>
       <c r="L17" s="15">
-        <v>1.904761904761</v>
+        <v>4.504504504504</v>
       </c>
       <c r="M17" s="15">
-        <v>84.482758620689</v>
+        <v>90.163934426229</v>
       </c>
       <c r="N17" s="15">
-        <v>50.704225352112</v>
+        <v>56.756756756756</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>60</v>
+        <v>54.545454545454</v>
       </c>
       <c r="I18" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J18" s="14">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K18" s="15">
-        <v>-33.928571428571</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="L18" s="15">
-        <v>-24.489795918367</v>
+        <v>-20</v>
       </c>
       <c r="M18" s="15">
-        <v>-53.164556962025</v>
+        <v>-51.807228915662</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.594202898550</v>
+        <v>-86.254295532646</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15">
-        <v>15.384615384615</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="F19" s="14">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G19" s="14">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H19" s="15">
-        <v>-32.307692307692</v>
+        <v>-28.169014084507</v>
       </c>
       <c r="I19" s="14">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="J19" s="14">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="K19" s="15">
-        <v>-1.408450704225</v>
+        <v>-2.155172413793</v>
       </c>
       <c r="L19" s="15">
-        <v>3.448275862068</v>
+        <v>6.572769953051</v>
       </c>
       <c r="M19" s="15">
-        <v>70.731707317073</v>
+        <v>73.282442748091</v>
       </c>
       <c r="N19" s="15">
-        <v>64.0625</v>
+        <v>65.693430656934</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E20" s="15">
-        <v>-20</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="F20" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G20" s="14">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H20" s="15">
-        <v>-40</v>
+        <v>-37.254901960784</v>
       </c>
       <c r="I20" s="14">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="J20" s="14">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="K20" s="15">
-        <v>-10.828025477707</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="L20" s="15">
-        <v>11.111111111111</v>
+        <v>15.384615384615</v>
       </c>
       <c r="M20" s="15">
-        <v>197.872340425532</v>
+        <v>163.157894736842</v>
       </c>
       <c r="N20" s="15">
-        <v>-76.973684210526</v>
+        <v>-76.958525345622</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D21" s="17">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E21" s="18">
-        <v>3.125</v>
+        <v>-19.565217391304</v>
       </c>
       <c r="F21" s="17">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="G21" s="17">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="H21" s="18">
-        <v>-26.785714285714</v>
+        <v>-21.264367816092</v>
       </c>
       <c r="I21" s="17">
-        <v>562</v>
+        <v>601</v>
       </c>
       <c r="J21" s="17">
-        <v>627</v>
+        <v>673</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.366826156299</v>
+        <v>-10.698365527488</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.919720767888</v>
+        <v>0.501672240802</v>
       </c>
       <c r="M21" s="18">
-        <v>45.974025974026</v>
+        <v>45.169082125603</v>
       </c>
       <c r="N21" s="18">
-        <v>-54.640839386602</v>
+        <v>-54.296577946768</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
         <v>11</v>
       </c>
       <c r="H23" s="15">
-        <v>-81.818181818181</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="I23" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J23" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K23" s="15">
-        <v>-69.565217391304</v>
+        <v>-56</v>
       </c>
       <c r="L23" s="15">
-        <v>-65</v>
+        <v>-54.166666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>-41.666666666666</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D24" s="14">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E24" s="15">
-        <v>-51.724137931034</v>
+        <v>-36.170212765957</v>
       </c>
       <c r="F24" s="14">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G24" s="14">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="H24" s="15">
-        <v>-20</v>
+        <v>-23.870967741935</v>
       </c>
       <c r="I24" s="14">
-        <v>440</v>
+        <v>470</v>
       </c>
       <c r="J24" s="14">
-        <v>441</v>
+        <v>488</v>
       </c>
       <c r="K24" s="15">
-        <v>-0.226757369614</v>
+        <v>-3.688524590163</v>
       </c>
       <c r="L24" s="15">
-        <v>-3.508771929824</v>
+        <v>-2.892561983471</v>
       </c>
       <c r="M24" s="15">
-        <v>10.275689223057</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>-32</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G25" s="14">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="H25" s="15">
-        <v>-17.582417582417</v>
+        <v>-5.128205128205</v>
       </c>
       <c r="I25" s="14">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="J25" s="14">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="K25" s="15">
-        <v>8.171206225680</v>
+        <v>9.926470588235</v>
       </c>
       <c r="L25" s="15">
-        <v>5.703422053231</v>
+        <v>7.553956834532</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="F26" s="14">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G26" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H26" s="15">
-        <v>34.210526315789</v>
+        <v>48.571428571428</v>
       </c>
       <c r="I26" s="14">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="J26" s="14">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="K26" s="15">
-        <v>16.993464052287</v>
+        <v>20.245398773006</v>
       </c>
       <c r="L26" s="15">
-        <v>0.561797752808</v>
+        <v>5.376344086021</v>
       </c>
       <c r="M26" s="15">
-        <v>49.166666666666</v>
+        <v>50.769230769230</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>3</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="14">
-        <v>4</v>
-      </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J27" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K27" s="15">
-        <v>66.666666666666</v>
+        <v>26.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>100</v>
+        <v>46.153846153846</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>4</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K28" s="15">
-        <v>-52.631578947368</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="L28" s="15">
-        <v>-66.666666666666</v>
+        <v>-58.620689655172</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,7 +1494,7 @@
         <v>-50</v>
       </c>
       <c r="L29" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M29" s="15">
         <v>100</v>
@@ -1535,7 +1535,7 @@
         <v>-50</v>
       </c>
       <c r="L30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
         <v>100</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-045pct.xlsx
+++ b/data/source/weekly/cs-en-us-045pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="I15" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K15" s="15">
-        <v>30.769230769230</v>
+        <v>20</v>
       </c>
       <c r="L15" s="15">
-        <v>88.888888888888</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>142.857142857143</v>
+        <v>157.142857142857</v>
       </c>
       <c r="N15" s="15">
-        <v>112.5</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
         <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="I16" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J16" s="14">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K16" s="15">
-        <v>-35.897435897435</v>
+        <v>-35.365853658536</v>
       </c>
       <c r="L16" s="15">
-        <v>-39.759036144578</v>
+        <v>-36.904761904761</v>
       </c>
       <c r="M16" s="15">
-        <v>-33.333333333333</v>
+        <v>-35.365853658536</v>
       </c>
       <c r="N16" s="15">
-        <v>-66.887417218543</v>
+        <v>-67.283950617283</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G17" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>36.363636363636</v>
+        <v>3.703703703703</v>
       </c>
       <c r="I17" s="14">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="J17" s="14">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="K17" s="15">
-        <v>0.869565217391</v>
+        <v>1.612903225806</v>
       </c>
       <c r="L17" s="15">
-        <v>4.504504504504</v>
+        <v>8.620689655172</v>
       </c>
       <c r="M17" s="15">
-        <v>90.163934426229</v>
+        <v>96.875</v>
       </c>
       <c r="N17" s="15">
-        <v>56.756756756756</v>
+        <v>59.493670886075</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,13 +1016,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>17</v>
@@ -1034,22 +1034,22 @@
         <v>54.545454545454</v>
       </c>
       <c r="I18" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J18" s="14">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K18" s="15">
-        <v>-31.034482758620</v>
+        <v>-31.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>-20</v>
+        <v>-21.153846153846</v>
       </c>
       <c r="M18" s="15">
-        <v>-51.807228915662</v>
+        <v>-53.932584269662</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.254295532646</v>
+        <v>-86.731391585760</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>16</v>
+      </c>
+      <c r="D19" s="14">
         <v>15</v>
       </c>
-      <c r="D19" s="14">
-        <v>19</v>
-      </c>
       <c r="E19" s="15">
-        <v>-21.052631578947</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G19" s="14">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="H19" s="15">
-        <v>-28.169014084507</v>
+        <v>-9.375</v>
       </c>
       <c r="I19" s="14">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="J19" s="14">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="K19" s="15">
-        <v>-2.155172413793</v>
+        <v>-1.214574898785</v>
       </c>
       <c r="L19" s="15">
-        <v>6.572769953051</v>
+        <v>8.444444444444</v>
       </c>
       <c r="M19" s="15">
-        <v>73.282442748091</v>
+        <v>71.830985915493</v>
       </c>
       <c r="N19" s="15">
-        <v>65.693430656934</v>
+        <v>64.864864864864</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E20" s="15">
-        <v>-41.176470588235</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F20" s="14">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G20" s="14">
         <v>51</v>
       </c>
       <c r="H20" s="15">
-        <v>-37.254901960784</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="I20" s="14">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="J20" s="14">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="K20" s="15">
-        <v>-13.793103448275</v>
+        <v>-15.508021390374</v>
       </c>
       <c r="L20" s="15">
-        <v>15.384615384615</v>
+        <v>11.267605633802</v>
       </c>
       <c r="M20" s="15">
-        <v>163.157894736842</v>
+        <v>172.413793103448</v>
       </c>
       <c r="N20" s="15">
-        <v>-76.958525345622</v>
+        <v>-77.200577200577</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E21" s="18">
-        <v>-19.565217391304</v>
+        <v>-15.555555555555</v>
       </c>
       <c r="F21" s="17">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G21" s="17">
         <v>174</v>
       </c>
       <c r="H21" s="18">
-        <v>-21.264367816092</v>
+        <v>-18.965517241379</v>
       </c>
       <c r="I21" s="17">
-        <v>601</v>
+        <v>641</v>
       </c>
       <c r="J21" s="17">
-        <v>673</v>
+        <v>718</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.698365527488</v>
+        <v>-10.724233983286</v>
       </c>
       <c r="L21" s="18">
-        <v>0.501672240802</v>
+        <v>1.746031746031</v>
       </c>
       <c r="M21" s="18">
-        <v>45.169082125603</v>
+        <v>45.022624434389</v>
       </c>
       <c r="N21" s="18">
-        <v>-54.296577946768</v>
+        <v>-54.279600570613</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="L22" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>3</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="14">
         <v>4</v>
       </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
-      <c r="E23" s="15">
-        <v>100</v>
-      </c>
-      <c r="F23" s="14">
-        <v>5</v>
-      </c>
       <c r="G23" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H23" s="15">
-        <v>-54.545454545454</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="I23" s="14">
         <v>11</v>
       </c>
       <c r="J23" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K23" s="15">
+        <v>-60.714285714285</v>
+      </c>
+      <c r="L23" s="15">
         <v>-56</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-54.166666666666</v>
       </c>
       <c r="M23" s="15">
         <v>-15.384615384615</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D24" s="14">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>-36.170212765957</v>
+        <v>233.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="G24" s="14">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="H24" s="15">
-        <v>-23.870967741935</v>
+        <v>-8.275862068965</v>
       </c>
       <c r="I24" s="14">
-        <v>470</v>
+        <v>510</v>
       </c>
       <c r="J24" s="14">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.688524590163</v>
+        <v>2</v>
       </c>
       <c r="L24" s="15">
-        <v>-2.892561983471</v>
+        <v>-1.162790697674</v>
       </c>
       <c r="M24" s="15">
-        <v>11.111111111111</v>
+        <v>10.869565217391</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>33.333333333333</v>
+        <v>187.5</v>
       </c>
       <c r="F25" s="14">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G25" s="14">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H25" s="15">
-        <v>-5.128205128205</v>
+        <v>18.571428571428</v>
       </c>
       <c r="I25" s="14">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="J25" s="14">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="K25" s="15">
-        <v>9.926470588235</v>
+        <v>15.357142857142</v>
       </c>
       <c r="L25" s="15">
-        <v>7.553956834532</v>
+        <v>6.600660066006</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>70</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F26" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G26" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H26" s="15">
-        <v>48.571428571428</v>
+        <v>55.555555555555</v>
       </c>
       <c r="I26" s="14">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="J26" s="14">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="K26" s="15">
-        <v>20.245398773006</v>
+        <v>20.930232558139</v>
       </c>
       <c r="L26" s="15">
-        <v>5.376344086021</v>
+        <v>6.122448979591</v>
       </c>
       <c r="M26" s="15">
-        <v>50.769230769230</v>
+        <v>49.640287769784</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F27" s="14">
         <v>3</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>2</v>
-      </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="I27" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J27" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>26.666666666666</v>
+        <v>17.647058823529</v>
       </c>
       <c r="L27" s="15">
-        <v>46.153846153846</v>
+        <v>53.846153846153</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F28" s="14">
+        <v>6</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="I28" s="14">
+        <v>13</v>
+      </c>
+      <c r="J28" s="14">
+        <v>26</v>
+      </c>
+      <c r="K28" s="15">
         <v>-50</v>
       </c>
-      <c r="F28" s="14">
-        <v>5</v>
-      </c>
-      <c r="G28" s="14">
-        <v>5</v>
-      </c>
-      <c r="H28" s="15">
-        <v>0</v>
-      </c>
-      <c r="I28" s="14">
-        <v>12</v>
-      </c>
-      <c r="J28" s="14">
-        <v>23</v>
-      </c>
-      <c r="K28" s="15">
-        <v>-47.826086956521</v>
-      </c>
       <c r="L28" s="15">
-        <v>-58.620689655172</v>
+        <v>-55.172413793103</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
